--- a/Config/GameConfig/Datas/commonItem.xlsx
+++ b/Config/GameConfig/Datas/commonItem.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Configs\GameConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F098D3-91C7-4076-A0C9-3113184CAD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414EB807-A9FA-4FBA-B6FF-7D4A80E8EBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -93,9 +93,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>item.EQuality</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
@@ -154,11 +151,16 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>WHITE</t>
+    <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>PURPLE</t>
+    <t>price</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -569,14 +571,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="5" max="5" width="52.25" customWidth="1"/>
+    <col min="6" max="6" width="52.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -590,10 +592,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -601,8 +606,9 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -613,66 +619,79 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1000001</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1000002</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
